--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>0</v>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>1612.5</v>
+        <v>1807.5</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>682.5</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E10" s="25" t="n">
         <v>1</v>
@@ -1170,7 +1170,7 @@
         <v>75</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="H10" s="26" t="n">
         <v>75</v>
@@ -1577,14 +1577,14 @@
       </c>
       <c r="C24" s="27" t="inlineStr"/>
       <c r="D24" s="28" t="n">
-        <v>107.5</v>
+        <v>120.5</v>
       </c>
       <c r="E24" s="27" t="inlineStr"/>
       <c r="F24" s="29" t="n">
         <v>2295</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>1612.5</v>
+        <v>1807.5</v>
       </c>
       <c r="H24" s="29" t="n">
         <v>1455</v>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="C29" s="32" t="n">
-        <v>0.9023255813953488</v>
+        <v>0.8049792531120332</v>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-157.5</v>
+        <v>-352.5</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C37" s="34" t="n">
-        <v>11268.65979381443</v>
+        <v>12631.38144329897</v>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>9656.159793814433</v>
+        <v>10823.88144329897</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" s="33" t="n">
-        <v>-1100.659793814433</v>
+        <v>-2463.381443298969</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>1807.5</v>
+        <v>2047.5</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>1455</v>
+        <v>1680</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>487.5</v>
+        <v>247.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E22" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="26" t="n">
         <v>225</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="C24" s="27" t="inlineStr"/>
       <c r="D24" s="28" t="n">
-        <v>120.5</v>
+        <v>136.5</v>
       </c>
       <c r="E24" s="27" t="inlineStr"/>
       <c r="F24" s="29" t="n">
         <v>2295</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>1807.5</v>
+        <v>2047.5</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>1455</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="C29" s="32" t="n">
-        <v>0.8049792531120332</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.6339869281045751</v>
+        <v>0.7320261437908496</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-352.5</v>
+        <v>-367.5</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>-840</v>
+        <v>-615</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C37" s="34" t="n">
-        <v>12631.38144329897</v>
+        <v>12392.25</v>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>10823.88144329897</v>
+        <v>10344.75</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" s="33" t="n">
-        <v>-2463.381443298969</v>
+        <v>-2224.25</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -12,9 +12,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'SPRINT0'!$A$1:$F$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$40</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -959,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1299,75 +1299,75 @@
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Implement APP Dashboard</t>
+          <t>Final Documentation</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>ainhoaaf</t>
+          <t>flaviaserret04 &amp; Tigre44 &amp; ainhoaaf &amp; marcc28 &amp; atnic15</t>
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>202.5</v>
+        <v>0</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>Implement APP Feed</t>
+          <t>Implement APP Dashboard</t>
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>flaviaserret04</t>
+          <t>ainhoaaf</t>
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="E16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>210</v>
+        <v>202.5</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Implement APP Profile</t>
+          <t>Implement APP Feed</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>ainhoaaf</t>
+          <t>flaviaserret04</t>
         </is>
       </c>
       <c r="D17" s="18" t="n">
@@ -1377,83 +1377,83 @@
         <v>1</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>210</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Implement Arduino/ESP32 IoT Sensor Node</t>
+          <t>Implement APP Profile</t>
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Tigre44 &amp; marcc28</t>
+          <t>ainhoaaf</t>
         </is>
       </c>
       <c r="D18" s="23" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>330</v>
+        <v>210</v>
       </c>
       <c r="H18" s="26" t="n">
-        <v>142.5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Implement Login System</t>
+          <t>Implement Arduino/ESP32 IoT Sensor Node</t>
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>flaviaserret04</t>
+          <t>Tigre44 &amp; marcc28</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>180</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>Implement Multilanguage on APP</t>
+          <t>Implement Login System</t>
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
@@ -1461,29 +1461,29 @@
         </is>
       </c>
       <c r="D20" s="23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Implement SignUp System</t>
+          <t>Implement Multilanguage on APP</t>
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
@@ -1491,319 +1491,349 @@
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E21" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>195</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>MockUp Figma</t>
+          <t>Implement SignUp System</t>
         </is>
       </c>
       <c r="B22" s="23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>marcc28</t>
+          <t>flaviaserret04</t>
         </is>
       </c>
       <c r="D22" s="23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>225</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
+          <t>MockUp Figma</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>marcc28</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>225</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>240</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
           <t>Risk Analysis</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B24" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>marcc28</t>
         </is>
       </c>
-      <c r="D23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="21" t="n">
+      <c r="D24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="26" t="n">
         <v>105</v>
       </c>
-      <c r="G23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="G24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 1</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B25" s="28" t="n">
         <v>153</v>
       </c>
-      <c r="C24" s="27" t="inlineStr"/>
-      <c r="D24" s="28" t="n">
+      <c r="C25" s="27" t="inlineStr"/>
+      <c r="D25" s="28" t="n">
         <v>136.5</v>
       </c>
-      <c r="E24" s="27" t="inlineStr"/>
-      <c r="F24" s="29" t="n">
+      <c r="E25" s="27" t="inlineStr"/>
+      <c r="F25" s="29" t="n">
         <v>2295</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G25" s="29" t="n">
         <v>2047.5</v>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="H25" s="29" t="n">
         <v>1680</v>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="n">
-        <v>0.8205128205128205</v>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.7320261437908496</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C31" s="33" t="n">
-        <v>-367.5</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>0.7320261437908496</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>-367.5</v>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C33" s="33" t="n">
         <v>-615</v>
       </c>
-      <c r="D32" s="31" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C37" s="34" t="n">
-        <v>12392.25</v>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>10344.75</v>
+        <v>12392.25</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="n">
+        <v>10344.75</v>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B39" s="31" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C39" s="33" t="n">
+      <c r="C40" s="33" t="n">
         <v>-2224.25</v>
       </c>
-      <c r="D39" s="31" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H23"/>
+  <autoFilter ref="A8:H24"/>
   <mergeCells count="5">
     <mergeCell ref="A1:J2"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E23">
+  <conditionalFormatting sqref="E9:E24">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>1680</v>
+        <v>1822.5</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>6.5</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="26" t="n">
         <v>142.5</v>
@@ -1293,7 +1293,7 @@
         <v>97.5</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="15">
@@ -1617,7 +1617,7 @@
         <v>2047.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>1680</v>
+        <v>1822.5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8901098901098901</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.7320261437908496</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>-367.5</v>
+        <v>-225</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-615</v>
+        <v>-472.5</v>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>12392.25</v>
+        <v>11423.30864197531</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>10344.75</v>
+        <v>9375.808641975309</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-2224.25</v>
+        <v>-1255.308641975309</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1179,7 +1179,7 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Cost evaluation of the Project on Sprint 1 + Project manager tasks (RACI Matrix...)</t>
+          <t>Cost evaluation of the Project on Sprint 1</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>2047.5</v>
+        <v>2152.5</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>1822.5</v>
+        <v>1927.5</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>247.5</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="26" t="n">
         <v>105</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="C25" s="27" t="inlineStr"/>
       <c r="D25" s="28" t="n">
-        <v>136.5</v>
+        <v>143.5</v>
       </c>
       <c r="E25" s="27" t="inlineStr"/>
       <c r="F25" s="29" t="n">
         <v>2295</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>2047.5</v>
+        <v>2152.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>1822.5</v>
+        <v>1927.5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.8901098901098901</v>
+        <v>0.8954703832752613</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8398692810457516</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-472.5</v>
+        <v>-367.5</v>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>11423.30864197531</v>
+        <v>11354.92607003891</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>9375.808641975309</v>
+        <v>9202.426070038911</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-1255.308641975309</v>
+        <v>-1186.92607003891</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>0</v>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2295</v>
+        <v>2505</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>2152.5</v>
+        <v>2422.5</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>1927.5</v>
+        <v>2137.5</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>142.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
@@ -1251,19 +1251,19 @@
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14">
@@ -1603,21 +1603,21 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C25" s="27" t="inlineStr"/>
       <c r="D25" s="28" t="n">
-        <v>143.5</v>
+        <v>161.5</v>
       </c>
       <c r="E25" s="27" t="inlineStr"/>
       <c r="F25" s="29" t="n">
-        <v>2295</v>
+        <v>2505</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>2152.5</v>
+        <v>2422.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>1927.5</v>
+        <v>2137.5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.8954703832752613</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.8398692810457516</v>
+        <v>0.8532934131736527</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>-225</v>
+        <v>-285</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>11354.92607003891</v>
+        <v>11523.73333333333</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>9202.426070038911</v>
+        <v>9101.233333333334</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-1186.92607003891</v>
+        <v>-1355.733333333333</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2505</v>
+        <v>2580</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>2422.5</v>
+        <v>2647.5</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>2137.5</v>
+        <v>2362.5</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>82.5</v>
+        <v>-67.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>225</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>0</v>
@@ -1603,21 +1603,21 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C25" s="27" t="inlineStr"/>
       <c r="D25" s="28" t="n">
-        <v>161.5</v>
+        <v>176.5</v>
       </c>
       <c r="E25" s="27" t="inlineStr"/>
       <c r="F25" s="29" t="n">
-        <v>2505</v>
+        <v>2580</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>2422.5</v>
+        <v>2647.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>2137.5</v>
+        <v>2362.5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8923512747875354</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.8532934131736527</v>
+        <v>0.9156976744186046</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-367.5</v>
+        <v>-217.5</v>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>11523.73333333333</v>
+        <v>11394.61587301587</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>9101.233333333334</v>
+        <v>8747.115873015873</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-1355.733333333333</v>
+        <v>-1226.615873015873</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>2362.5</v>
+        <v>2437.5</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>75</v>
@@ -1323,7 +1323,7 @@
         <v>75</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -1617,7 +1617,7 @@
         <v>2647.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>2362.5</v>
+        <v>2437.5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.8923512747875354</v>
+        <v>0.9206798866855525</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.9156976744186046</v>
+        <v>0.9447674418604651</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>-285</v>
+        <v>-210</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-217.5</v>
+        <v>-142.5</v>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>11394.61587301587</v>
+        <v>11044.01230769231</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>8747.115873015873</v>
+        <v>8396.512307692308</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-1226.615873015873</v>
+        <v>-876.0123076923077</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>2437.5</v>
+        <v>2409</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>22</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F19" s="21" t="n">
         <v>285</v>
@@ -1443,7 +1443,7 @@
         <v>330</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>142.5</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
@@ -1617,7 +1617,7 @@
         <v>2647.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>2437.5</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.9206798866855525</v>
+        <v>0.909915014164306</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.9447674418604651</v>
+        <v>0.9337209302325581</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>-210</v>
+        <v>-238.5</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-142.5</v>
+        <v>-171</v>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>11044.01230769231</v>
+        <v>11174.6699875467</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>8396.512307692308</v>
+        <v>8527.1699875467</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-876.0123076923077</v>
+        <v>-1006.6699875467</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>2409</v>
+        <v>2390</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>22</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F19" s="21" t="n">
         <v>285</v>
@@ -1443,7 +1443,7 @@
         <v>330</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
@@ -1617,7 +1617,7 @@
         <v>2647.5</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>2409</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.909915014164306</v>
+        <v>0.902738432483475</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>0.9337209302325581</v>
+        <v>0.9263565891472868</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>-238.5</v>
+        <v>-257.5</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-171</v>
+        <v>-190</v>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>11174.6699875467</v>
+        <v>11263.50627615063</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>8527.1699875467</v>
+        <v>8616.006276150627</v>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C40" s="33" t="n">
-        <v>-1006.6699875467</v>
+        <v>-1095.506276150628</v>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -9,12 +9,16 @@
   <sheets>
     <sheet name="SPRINT0" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="SPRINT1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SPRINT2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'SPRINT0'!$A$1:$F$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -95,7 +99,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +134,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -262,10 +271,16 @@
     <xf numFmtId="2" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -959,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1033,7 +1048,7 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2580</v>
+        <v>2295</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
@@ -1041,7 +1056,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>2647.5</v>
+        <v>2317.5</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1049,7 +1064,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>2390</v>
+        <v>2295</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1072,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>-67.5</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1419,41 +1434,41 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Implement Arduino/ESP32 IoT Sensor Node</t>
+          <t>Implement Login System</t>
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>Tigre44 &amp; marcc28</t>
+          <t>flaviaserret04</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>330</v>
+        <v>180</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>Implement Login System</t>
+          <t>Implement Multilanguage on APP</t>
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
@@ -1461,29 +1476,29 @@
         </is>
       </c>
       <c r="D20" s="23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Implement Multilanguage on APP</t>
+          <t>Implement SignUp System</t>
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
@@ -1491,59 +1506,59 @@
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E21" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>60</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>Implement SignUp System</t>
+          <t>MockUp Figma</t>
         </is>
       </c>
       <c r="B22" s="23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>flaviaserret04</t>
+          <t>marcc28</t>
         </is>
       </c>
       <c r="D22" s="23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>MockUp Figma</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
@@ -1551,289 +1566,704 @@
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E23" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>240</v>
+        <v>105</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>225</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Risk Analysis</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>marcc28</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="26" t="n">
-        <v>105</v>
-      </c>
-      <c r="G24" s="26" t="n">
-        <v>105</v>
-      </c>
-      <c r="H24" s="26" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 1</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
-        <v>172</v>
-      </c>
-      <c r="C25" s="27" t="inlineStr"/>
-      <c r="D25" s="28" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="E25" s="27" t="inlineStr"/>
-      <c r="F25" s="29" t="n">
-        <v>2580</v>
-      </c>
-      <c r="G25" s="29" t="n">
-        <v>2647.5</v>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>2390</v>
-      </c>
+      <c r="B24" s="28" t="n">
+        <v>153</v>
+      </c>
+      <c r="C24" s="27" t="inlineStr"/>
+      <c r="D24" s="28" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="E24" s="27" t="inlineStr"/>
+      <c r="F24" s="29" t="n">
+        <v>2295</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <v>2317.5</v>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>CPI</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>EV / AC</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n">
+        <v>0.9902912621359223</v>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>CPI</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="n">
-        <v>0.902738432483475</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>1</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
-          <t>Cost overrun</t>
+          <t>On or ahead of plan</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="n">
-        <v>0.9263565891472868</v>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>-22.5</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Unfavourable</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="n">
-        <v>-257.5</v>
+          <t>EV - PV</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>EV - PV</t>
-        </is>
-      </c>
-      <c r="C33" s="33" t="n">
-        <v>-190</v>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Unfavourable</t>
-        </is>
-      </c>
+          <t>Favourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>EAC</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>BAC / CPI</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="n">
+        <v>10267.6862745098</v>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>EAC</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C38" s="34" t="n">
-        <v>11263.50627615063</v>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>7950.186274509804</v>
       </c>
       <c r="D38" s="31" t="inlineStr">
         <is>
-          <t>Estimated total cost</t>
+          <t>Estimated remaining cost</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="30" t="inlineStr">
         <is>
+          <t>VAC</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>BAC - EAC</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="n">
+        <v>-99.68627450980392</v>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>Expected budget variance</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:H23"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A4:J4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E9:E23">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="004472C4"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004472C4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COST CONTROL - SPRINT 2</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="8" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Main cost values</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>10168</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>330</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>PV - AC</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>PV (€)</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>AC (€)</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>EV (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Implement Arduino/ESP32 IoT Sensor Node</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Tigre44 &amp; marcc28</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>285</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>330</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL SPRINT 2</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="C10" s="27" t="inlineStr"/>
+      <c r="D10" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="27" t="inlineStr"/>
+      <c r="F10" s="29" t="n">
+        <v>285</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>330</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>CPI</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>EV / AC</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>0.2878787878787879</v>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Cost overrun</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Behind plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>EV - PV</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>-190</v>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>EAC</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>BAC / CPI</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>35320.42105263158</v>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Estimated total cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
           <t>ETC</t>
         </is>
       </c>
-      <c r="B39" s="31" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>EAC - AC</t>
         </is>
       </c>
-      <c r="C39" s="34" t="n">
-        <v>8616.006276150627</v>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
+      <c r="C24" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>Estimated remaining cost</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B40" s="31" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C40" s="33" t="n">
-        <v>-1095.506276150628</v>
-      </c>
-      <c r="D40" s="31" t="inlineStr">
+      <c r="C25" s="34" t="n">
+        <v>-25152.42105263158</v>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H24"/>
+  <autoFilter ref="A8:H9"/>
   <mergeCells count="5">
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E24">
+  <conditionalFormatting sqref="E9">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$26</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2027,243 +2027,273 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Weather alerts for the current garden</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>atnic15</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B11" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C10" s="27" t="inlineStr"/>
-      <c r="D10" s="28" t="n">
+      <c r="C11" s="27" t="inlineStr"/>
+      <c r="D11" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E10" s="27" t="inlineStr"/>
-      <c r="F10" s="29" t="n">
+      <c r="E11" s="27" t="inlineStr"/>
+      <c r="F11" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G11" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H10" s="29" t="n">
+      <c r="H11" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C19" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D18" s="31" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C24" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C25" s="34" t="n">
+      <c r="C26" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D26" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H9"/>
+  <autoFilter ref="A8:H10"/>
   <mergeCells count="5">
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9">
+  <conditionalFormatting sqref="E9:E10">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$27</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2029,17 +2029,13 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Weather alerts for the current garden</t>
+          <t>Task list for the current garden</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>atnic15</t>
-        </is>
-      </c>
+      <c r="C10" s="24" t="inlineStr"/>
       <c r="D10" s="23" t="n">
         <v>0</v>
       </c>
@@ -2057,243 +2053,273 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Weather alerts for the current garden</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>atnic15</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B12" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C11" s="27" t="inlineStr"/>
-      <c r="D11" s="28" t="n">
+      <c r="C12" s="27" t="inlineStr"/>
+      <c r="D12" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E11" s="27" t="inlineStr"/>
-      <c r="F11" s="29" t="n">
+      <c r="E12" s="27" t="inlineStr"/>
+      <c r="F12" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G12" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H11" s="29" t="n">
+      <c r="H12" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C17" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n">
+      <c r="C20" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C25" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C26" s="34" t="n">
+      <c r="C27" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D26" s="31" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H10"/>
+  <autoFilter ref="A8:H11"/>
   <mergeCells count="5">
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E10">
+  <conditionalFormatting sqref="E9:E11">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$28</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2029,7 +2029,7 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Task list for the current garden</t>
+          <t>Plant photo diagnosis</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
@@ -2055,17 +2055,13 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Weather alerts for the current garden</t>
+          <t>Task list for the current garden</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>atnic15</t>
-        </is>
-      </c>
+      <c r="C11" s="19" t="inlineStr"/>
       <c r="D11" s="18" t="n">
         <v>0</v>
       </c>
@@ -2083,243 +2079,273 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Weather alerts for the current garden</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>atnic15</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B13" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C12" s="27" t="inlineStr"/>
-      <c r="D12" s="28" t="n">
+      <c r="C13" s="27" t="inlineStr"/>
+      <c r="D13" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E12" s="27" t="inlineStr"/>
-      <c r="F12" s="29" t="n">
+      <c r="E13" s="27" t="inlineStr"/>
+      <c r="F13" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G13" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="H13" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C17" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C21" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D20" s="31" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C25" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C26" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D26" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C27" s="34" t="n">
+      <c r="C28" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H11"/>
+  <autoFilter ref="A8:H12"/>
   <mergeCells count="5">
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E11">
+  <conditionalFormatting sqref="E9:E12">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2029,13 +2029,17 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Plant photo diagnosis</t>
+          <t>Marked redirection</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="24" t="inlineStr"/>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>flaviaserret04</t>
+        </is>
+      </c>
       <c r="D10" s="23" t="n">
         <v>0</v>
       </c>
@@ -2055,7 +2059,7 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Task list for the current garden</t>
+          <t>Plant photo diagnosis</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
@@ -2081,271 +2085,297 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
+          <t>Task list for the current garden</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="inlineStr"/>
+      <c r="D12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
           <t>Weather alerts for the current garden</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="B13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>atnic15</t>
         </is>
       </c>
-      <c r="D12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="D13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
+      <c r="B14" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C13" s="27" t="inlineStr"/>
-      <c r="D13" s="28" t="n">
+      <c r="C14" s="27" t="inlineStr"/>
+      <c r="D14" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E13" s="27" t="inlineStr"/>
-      <c r="F13" s="29" t="n">
+      <c r="E14" s="27" t="inlineStr"/>
+      <c r="F14" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G14" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H13" s="29" t="n">
+      <c r="H14" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C22" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D22" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D26" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C27" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C28" s="34" t="n">
+      <c r="C29" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D28" s="31" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H12"/>
+  <autoFilter ref="A8:H13"/>
   <mergeCells count="5">
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A25:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E12">
+  <conditionalFormatting sqref="E9:E13">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2059,13 +2059,17 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Plant photo diagnosis</t>
+          <t>Planning commitment from Sprint 2</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Tigre44 &amp; atnic15</t>
+        </is>
+      </c>
       <c r="D11" s="18" t="n">
         <v>0</v>
       </c>
@@ -2085,7 +2089,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Task list for the current garden</t>
+          <t>Plant photo diagnosis</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
@@ -2111,271 +2115,297 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
+          <t>Task list for the current garden</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
           <t>Weather alerts for the current garden</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="B14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>atnic15</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="D14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B15" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C14" s="27" t="inlineStr"/>
-      <c r="D14" s="28" t="n">
+      <c r="C15" s="27" t="inlineStr"/>
+      <c r="D15" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E14" s="27" t="inlineStr"/>
-      <c r="F14" s="29" t="n">
+      <c r="E15" s="27" t="inlineStr"/>
+      <c r="F15" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G15" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="H15" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C19" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C22" s="34" t="n">
+      <c r="C23" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D22" s="31" t="inlineStr">
+      <c r="D23" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C28" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D28" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C29" s="34" t="n">
+      <c r="C30" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H13"/>
+  <autoFilter ref="A8:H14"/>
   <mergeCells count="5">
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A25:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E13">
+  <conditionalFormatting sqref="E9:E14">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1999,67 +1999,63 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Implement Arduino/ESP32 IoT Sensor Node</t>
+          <t>AI crop recommendation</t>
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Tigre44 &amp; marcc28</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" s="19" t="inlineStr"/>
       <c r="D9" s="18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Marked redirection</t>
+          <t>Implement Arduino/ESP32 IoT Sensor Node</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>flaviaserret04</t>
+          <t>Tigre44 &amp; marcc28</t>
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Planning commitment from Sprint 2</t>
+          <t>Marked redirection</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
@@ -2067,7 +2063,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Tigre44 &amp; atnic15</t>
+          <t>flaviaserret04</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
@@ -2089,13 +2085,17 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Plant photo diagnosis</t>
+          <t>Planning commitment from Sprint 2</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="24" t="inlineStr"/>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Tigre44 &amp; atnic15</t>
+        </is>
+      </c>
       <c r="D12" s="23" t="n">
         <v>0</v>
       </c>
@@ -2115,7 +2115,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Task list for the current garden</t>
+          <t>Plant photo diagnosis</t>
         </is>
       </c>
       <c r="B13" s="18" t="n">
@@ -2141,271 +2141,297 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
+          <t>Task list for the current garden</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="inlineStr"/>
+      <c r="D14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
           <t>Weather alerts for the current garden</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="B15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>atnic15</t>
         </is>
       </c>
-      <c r="D14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="D15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B16" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C15" s="27" t="inlineStr"/>
-      <c r="D15" s="28" t="n">
+      <c r="C16" s="27" t="inlineStr"/>
+      <c r="D16" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E15" s="27" t="inlineStr"/>
-      <c r="F15" s="29" t="n">
+      <c r="E16" s="27" t="inlineStr"/>
+      <c r="F16" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G16" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H15" s="29" t="n">
+      <c r="H16" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D20" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C22" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C23" s="34" t="n">
+      <c r="C24" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C29" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C30" s="34" t="n">
+      <c r="C31" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D30" s="31" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H14"/>
+  <autoFilter ref="A8:H15"/>
   <mergeCells count="5">
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E14">
+  <conditionalFormatting sqref="E9:E15">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SPRINT1'!$A$8:$H$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'SPRINT1'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'SPRINT1'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT2'!$A$8:$H$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'SPRINT2'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SPRINT2'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2141,13 +2141,17 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>Task list for the current garden</t>
+          <t>Security of the data, the broker and the API</t>
         </is>
       </c>
       <c r="B14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="24" t="inlineStr"/>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>flaviaserret04</t>
+        </is>
+      </c>
       <c r="D14" s="23" t="n">
         <v>0</v>
       </c>
@@ -2167,271 +2171,297 @@
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
+          <t>Task list for the current garden</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
           <t>Weather alerts for the current garden</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="B16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>atnic15</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="D16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>TOTAL SPRINT 2</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B17" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="27" t="inlineStr"/>
-      <c r="D16" s="28" t="n">
+      <c r="C17" s="27" t="inlineStr"/>
+      <c r="D17" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="E16" s="27" t="inlineStr"/>
-      <c r="F16" s="29" t="n">
+      <c r="E17" s="27" t="inlineStr"/>
+      <c r="F17" s="29" t="n">
         <v>285</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G17" s="29" t="n">
         <v>330</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H17" s="29" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>EV / AC</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="n">
-        <v>0.2878787878787879</v>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>EV / PV</t>
+          <t>EV / AC</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2878787878787879</v>
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>Behind plan</t>
+          <t>Cost overrun</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>EV - AC</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="n">
-        <v>-235</v>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Unfavourable</t>
+          <t>Behind plan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>-235</v>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Unfavourable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>EV - PV</t>
         </is>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C25" s="34" t="n">
         <v>-190</v>
       </c>
-      <c r="D24" s="31" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>Unfavourable</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>EAC</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="inlineStr">
-        <is>
-          <t>BAC / CPI</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>35320.42105263158</v>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>EAC - AC</t>
+          <t>BAC / CPI</t>
         </is>
       </c>
       <c r="C30" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>35320.42105263158</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
-          <t>Estimated remaining cost</t>
+          <t>Estimated total cost</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>EAC - AC</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>34990.42105263158</v>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Estimated remaining cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
           <t>VAC</t>
         </is>
       </c>
-      <c r="B31" s="31" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>BAC - EAC</t>
         </is>
       </c>
-      <c r="C31" s="34" t="n">
+      <c r="C32" s="34" t="n">
         <v>-25152.42105263158</v>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>Expected budget variance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H15"/>
+  <autoFilter ref="A8:H16"/>
   <mergeCells count="5">
     <mergeCell ref="A1:J2"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E15">
+  <conditionalFormatting sqref="E9:E16">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>flaviaserret04</t>
+          <t>flaviaserret04 &amp; marcc28</t>
         </is>
       </c>
       <c r="D14" s="23" t="n">

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -2005,7 +2005,11 @@
       <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>flaviaserret04</t>
+        </is>
+      </c>
       <c r="D9" s="18" t="n">
         <v>0</v>
       </c>
@@ -2121,7 +2125,11 @@
       <c r="B13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>atnic15</t>
+        </is>
+      </c>
       <c r="D13" s="18" t="n">
         <v>0</v>
       </c>
@@ -2177,7 +2185,11 @@
       <c r="B15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>ainhoaaf</t>
+        </is>
+      </c>
       <c r="D15" s="18" t="n">
         <v>0</v>
       </c>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>flaviaserret04 &amp; marcc28</t>
+          <t>marcc28</t>
         </is>
       </c>
       <c r="D14" s="23" t="n">

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H16" s="26" t="n">
         <v>0</v>
@@ -2243,18 +2243,18 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C17" s="27" t="inlineStr"/>
       <c r="D17" s="28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E17" s="27" t="inlineStr"/>
       <c r="F17" s="29" t="n">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="H17" s="29" t="n">
         <v>95</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>0.2878787878787879</v>
+        <v>0.2533333333333334</v>
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2753623188405797</v>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>-235</v>
+        <v>-280</v>
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>-190</v>
+        <v>-250</v>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="C30" s="36" t="n">
-        <v>35320.42105263158</v>
+        <v>40136.84210526316</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C31" s="36" t="n">
-        <v>34990.42105263158</v>
+        <v>39761.84210526316</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="C32" s="34" t="n">
-        <v>-25152.42105263158</v>
+        <v>-29968.84210526316</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>

--- a/reports/costes.xlsx
+++ b/reports/costes.xlsx
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="H16" s="26" t="n">
         <v>0</v>
@@ -2243,18 +2243,18 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C17" s="27" t="inlineStr"/>
       <c r="D17" s="28" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E17" s="27" t="inlineStr"/>
       <c r="F17" s="29" t="n">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="H17" s="29" t="n">
         <v>95</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>0.2533333333333334</v>
+        <v>0.2183908045977012</v>
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>0.2753623188405797</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>-280</v>
+        <v>-340</v>
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>-250</v>
+        <v>-310</v>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="C30" s="36" t="n">
-        <v>40136.84210526316</v>
+        <v>46558.73684210526</v>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C31" s="36" t="n">
-        <v>39761.84210526316</v>
+        <v>46123.73684210526</v>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="C32" s="34" t="n">
-        <v>-29968.84210526316</v>
+        <v>-36390.73684210526</v>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
